--- a/KURIKULUM2026_REVISI/043_MATRIKS_CPL_CPMK_BoK_DAN_BOUNDARY_GUARDRAILS.xlsx
+++ b/KURIKULUM2026_REVISI/043_MATRIKS_CPL_CPMK_BoK_DAN_BOUNDARY_GUARDRAILS.xlsx
@@ -23834,7 +23834,7 @@
     <row r="877" ht="16" customHeight="1">
       <c r="A877" s="8" t="inlineStr">
         <is>
-          <t>STI-626</t>
+          <t>STI-726</t>
         </is>
       </c>
       <c r="B877" s="7" t="inlineStr">
@@ -23871,7 +23871,7 @@
     <row r="878" ht="16" customHeight="1">
       <c r="A878" s="10" t="inlineStr">
         <is>
-          <t>STI-627</t>
+          <t>STI-727</t>
         </is>
       </c>
       <c r="B878" s="9" t="inlineStr">
@@ -23909,7 +23909,7 @@
     <row r="880" ht="20" customHeight="1">
       <c r="A880" s="3" t="inlineStr">
         <is>
-          <t>STI-626 — Deep Learning &amp; Neural Networks</t>
+          <t>STI-726 — Deep Learning &amp; Neural Networks</t>
         </is>
       </c>
       <c r="B880" s="4" t="n"/>
@@ -24032,7 +24032,7 @@
     <row r="887" ht="20" customHeight="1">
       <c r="A887" s="3" t="inlineStr">
         <is>
-          <t>STI-626 — Deep Learning &amp; Neural Networks</t>
+          <t>STI-726 — Deep Learning &amp; Neural Networks</t>
         </is>
       </c>
       <c r="B887" s="4" t="n"/>
@@ -24243,7 +24243,7 @@
     <row r="898" ht="20" customHeight="1">
       <c r="A898" s="3" t="inlineStr">
         <is>
-          <t>STI-626 — Deep Learning &amp; Neural Networks</t>
+          <t>STI-726 — Deep Learning &amp; Neural Networks</t>
         </is>
       </c>
       <c r="B898" s="4" t="n"/>
@@ -24886,7 +24886,7 @@
     <row r="917" ht="20" customHeight="1">
       <c r="A917" s="3" t="inlineStr">
         <is>
-          <t>STI-627 — Digital Platform Engineering</t>
+          <t>STI-727 — Digital Platform Engineering</t>
         </is>
       </c>
       <c r="B917" s="4" t="n"/>
@@ -25009,7 +25009,7 @@
     <row r="924" ht="20" customHeight="1">
       <c r="A924" s="3" t="inlineStr">
         <is>
-          <t>STI-627 — Digital Platform Engineering</t>
+          <t>STI-727 — Digital Platform Engineering</t>
         </is>
       </c>
       <c r="B924" s="4" t="n"/>
@@ -25220,7 +25220,7 @@
     <row r="935" ht="20" customHeight="1">
       <c r="A935" s="3" t="inlineStr">
         <is>
-          <t>STI-627 — Digital Platform Engineering</t>
+          <t>STI-727 — Digital Platform Engineering</t>
         </is>
       </c>
       <c r="B935" s="4" t="n"/>
@@ -25913,7 +25913,7 @@
     <row r="956" ht="16" customHeight="1">
       <c r="A956" s="8" t="inlineStr">
         <is>
-          <t>STI-624</t>
+          <t>STI-726</t>
         </is>
       </c>
       <c r="B956" s="7" t="inlineStr">
@@ -25950,7 +25950,7 @@
     <row r="957" ht="16" customHeight="1">
       <c r="A957" s="10" t="inlineStr">
         <is>
-          <t>STI-625</t>
+          <t>STI-727</t>
         </is>
       </c>
       <c r="B957" s="9" t="inlineStr">
@@ -26002,7 +26002,7 @@
       </c>
       <c r="D958" s="7" t="inlineStr">
         <is>
-          <t>STI-627, MKU-204</t>
+          <t>STI-727, MKU-204</t>
         </is>
       </c>
       <c r="E958" s="7" t="inlineStr">
@@ -26025,7 +26025,7 @@
     <row r="960" ht="20" customHeight="1">
       <c r="A960" s="3" t="inlineStr">
         <is>
-          <t>STI-624 — Integrasi Layanan Cerdas Berbasis AI</t>
+          <t>STI-726 — Integrasi Layanan Cerdas Berbasis AI</t>
         </is>
       </c>
       <c r="B960" s="4" t="n"/>
@@ -26148,7 +26148,7 @@
     <row r="967" ht="20" customHeight="1">
       <c r="A967" s="3" t="inlineStr">
         <is>
-          <t>STI-624 — Integrasi Layanan Cerdas Berbasis AI</t>
+          <t>STI-726 — Integrasi Layanan Cerdas Berbasis AI</t>
         </is>
       </c>
       <c r="B967" s="4" t="n"/>
@@ -26359,7 +26359,7 @@
     <row r="978" ht="20" customHeight="1">
       <c r="A978" s="3" t="inlineStr">
         <is>
-          <t>STI-624 — Integrasi Layanan Cerdas Berbasis AI</t>
+          <t>STI-726 — Integrasi Layanan Cerdas Berbasis AI</t>
         </is>
       </c>
       <c r="B978" s="4" t="n"/>
@@ -27002,7 +27002,7 @@
     <row r="997" ht="20" customHeight="1">
       <c r="A997" s="3" t="inlineStr">
         <is>
-          <t>STI-625 — Smart City &amp; Pemerintahan Digital</t>
+          <t>STI-727 — Smart City &amp; Pemerintahan Digital</t>
         </is>
       </c>
       <c r="B997" s="4" t="n"/>
@@ -27125,7 +27125,7 @@
     <row r="1004" ht="20" customHeight="1">
       <c r="A1004" s="3" t="inlineStr">
         <is>
-          <t>STI-625 — Smart City &amp; Pemerintahan Digital</t>
+          <t>STI-727 — Smart City &amp; Pemerintahan Digital</t>
         </is>
       </c>
       <c r="B1004" s="4" t="n"/>
@@ -27336,7 +27336,7 @@
     <row r="1015" ht="20" customHeight="1">
       <c r="A1015" s="3" t="inlineStr">
         <is>
-          <t>STI-625 — Smart City &amp; Pemerintahan Digital</t>
+          <t>STI-727 — Smart City &amp; Pemerintahan Digital</t>
         </is>
       </c>
       <c r="B1015" s="4" t="n"/>
@@ -34972,7 +34972,7 @@
       </c>
       <c r="E1293" s="9" t="inlineStr">
         <is>
-          <t>STI-413, STI-624 Integrasi AI</t>
+          <t>STI-413, STI-726 Integrasi AI</t>
         </is>
       </c>
       <c r="F1293" s="9" t="inlineStr">
@@ -35056,7 +35056,7 @@
       </c>
       <c r="E1295" s="9" t="inlineStr">
         <is>
-          <t>STI-626, STI-521 IoT</t>
+          <t>STI-726, STI-521 IoT</t>
         </is>
       </c>
       <c r="F1295" s="9" t="inlineStr">
